--- a/11/static/temp/sample.xlsx
+++ b/11/static/temp/sample.xlsx
@@ -419,24 +419,24 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>42 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
+          <t>42 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>124 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
+          <t>2022-05-26 21:34:18.402000 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2022-05-26 21:34:18.402000 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
+          <t>124 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
+          <t>2 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
         </is>
       </c>
     </row>

--- a/11/static/temp/sample.xlsx
+++ b/11/static/temp/sample.xlsx
@@ -413,46 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>42 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2022-05-26 21:34:18.402000 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>124 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2 Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan Bogdan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>None Bogdan</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>None Bogdan</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>